--- a/docs/oc-mensuales/suministro-de-combustibles/may-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2450.88</v>
+        <v>2436.19</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5013.16</v>
+        <v>4983.11</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>11140.35</v>
+        <v>11073.58</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17935.96</v>
+        <v>17828.47</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3342.1</v>
+        <v>3322.08</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2450.88</v>
+        <v>2436.19</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7798.24</v>
+        <v>7751.51</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2361.75</v>
+        <v>2347.6</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2359.12</v>
+        <v>2344.99</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>55701.75</v>
+        <v>55367.92</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5570.17</v>
+        <v>5536.79</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7909.65</v>
+        <v>7862.24</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>23951.75</v>
+        <v>23808.21</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4623.25</v>
+        <v>4595.54</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3342.1</v>
+        <v>3322.08</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5570.17</v>
+        <v>5536.79</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3899.12</v>
+        <v>3875.75</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>27850.87</v>
+        <v>27683.96</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8355.26</v>
+        <v>8305.190000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2450.88</v>
+        <v>2436.19</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2339.47</v>
+        <v>2325.45</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>17267.54</v>
+        <v>17164.06</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3342.1</v>
+        <v>3322.08</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>11140.35</v>
+        <v>11073.58</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2785.09</v>
+        <v>2768.4</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>16710.52</v>
+        <v>16610.38</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5570.17</v>
+        <v>5536.79</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4456.14</v>
+        <v>4429.43</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4233.33</v>
+        <v>4207.96</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>22280.7</v>
+        <v>22147.17</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4010.53</v>
+        <v>3986.49</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5570.17</v>
+        <v>5536.79</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3342.1</v>
+        <v>3322.08</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4456.14</v>
+        <v>4429.43</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3342.1</v>
+        <v>3322.08</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3342.1</v>
+        <v>3296.67</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2450.88</v>
+        <v>2417.56</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>22280.7</v>
+        <v>21977.78</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8791.110000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2450.88</v>
+        <v>2417.56</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4456.14</v>
+        <v>4395.56</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2427.58</v>
+        <v>2394.57</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2450.88</v>
+        <v>2417.56</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7798.24</v>
+        <v>7692.22</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3342.1</v>
+        <v>3296.67</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8791.110000000001</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>22280.7</v>
+        <v>21977.78</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3342.1</v>
+        <v>3296.67</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3342.1</v>
+        <v>3296.67</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>23135.28</v>
+        <v>22820.74</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5639.47</v>
+        <v>5562.8</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2988.84</v>
+        <v>2948.21</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3899.12</v>
+        <v>3846.11</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8791.110000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2785.09</v>
+        <v>2747.22</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2450.88</v>
+        <v>2417.56</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7352.63</v>
+        <v>7252.67</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>6461.4</v>
+        <v>6373.56</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>12796.92</v>
+        <v>12622.94</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5570.17</v>
+        <v>5494.45</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3007.89</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2339.47</v>
+        <v>2307.67</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2785.09</v>
+        <v>2747.22</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7954.21</v>
+        <v>7846.07</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>11140.35</v>
+        <v>10988.89</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>37492.4</v>
+        <v>36982.67</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5570.17</v>
+        <v>5494.45</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>11140.35</v>
+        <v>10988.89</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4456.14</v>
+        <v>4395.56</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2785.09</v>
+        <v>2747.22</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>6007.61</v>
+        <v>5925.93</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5570.17</v>
+        <v>5494.45</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4260.21</v>
+        <v>4202.29</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5570.17</v>
+        <v>5494.45</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>11140.35</v>
+        <v>10988.89</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2785.09</v>
+        <v>2747.22</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2785.09</v>
+        <v>2761.33</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3342.1</v>
+        <v>3313.6</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2748.91</v>
+        <v>2725.46</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4456.14</v>
+        <v>4418.13</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>11140.35</v>
+        <v>11045.33</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2359.12</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4456.14</v>
+        <v>4418.13</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10026.31</v>
+        <v>9940.799999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7798.24</v>
+        <v>7731.73</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6684.21</v>
+        <v>6627.2</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>21588.18</v>
+        <v>21404.05</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5570.17</v>
+        <v>5522.67</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8228.48</v>
+        <v>8158.29</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7798.24</v>
+        <v>7731.73</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>11140.35</v>
+        <v>11045.33</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5570.17</v>
+        <v>5522.67</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4456.14</v>
+        <v>4418.13</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>16710.52</v>
+        <v>16568</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3899.12</v>
+        <v>3865.87</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2785.09</v>
+        <v>2761.33</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>11140.35</v>
+        <v>11045.33</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>28519.29</v>
+        <v>28276.04</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>14254.08</v>
+        <v>14132.5</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3342.1</v>
+        <v>3313.6</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>10026.31</v>
+        <v>9940.799999999999</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4456.14</v>
+        <v>4418.13</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8996.26</v>
+        <v>8919.530000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3342.1</v>
+        <v>3313.6</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>16710.52</v>
+        <v>16568</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3899.12</v>
+        <v>3865.87</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3453.51</v>
+        <v>3424.05</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>12796.92</v>
+        <v>12687.77</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>38991.22</v>
+        <v>38658.66</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>11140.35</v>
+        <v>11045.33</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2785.09</v>
+        <v>2761.33</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>36763.15</v>
+        <v>36449.59</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>22280.7</v>
+        <v>22090.66</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4790.35</v>
+        <v>4749.49</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>21166.66</v>
+        <v>20986.13</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2339.47</v>
+        <v>2319.52</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3342.1</v>
+        <v>3313.6</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>14482.45</v>
+        <v>14358.93</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3342.1</v>
+        <v>3313.6</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4456.14</v>
+        <v>4418.13</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>75754.38</v>
+        <v>75108.24000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3119.3</v>
+        <v>3092.69</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>4456.14</v>
+        <v>4418.13</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>7464.03</v>
+        <v>7400.37</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>76868.41</v>
+        <v>76212.78</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3329.85</v>
+        <v>3301.45</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>44561.4</v>
+        <v>44181.32</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6313.43</v>
+        <v>6347.43</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2359.53</v>
+        <v>2372.23</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>7176.75</v>
+        <v>7215.4</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>8382.780000000001</v>
+        <v>8427.92</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7628.91</v>
+        <v>7669.99</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>10026.31</v>
+        <v>10080.31</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>22280.7</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>15596.49</v>
+        <v>15680.48</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4456.14</v>
+        <v>4480.14</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>5570.17</v>
+        <v>5600.17</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2361.75</v>
+        <v>2374.47</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2450.88</v>
+        <v>2464.07</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6684.21</v>
+        <v>6720.2</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>27850.87</v>
+        <v>28000.85</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>22280.7</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>11140.35</v>
+        <v>11200.34</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>6684.21</v>
+        <v>6720.2</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5570.17</v>
+        <v>5600.17</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>17920.85</v>
+        <v>18017.36</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>5013.16</v>
+        <v>5040.15</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>11140.35</v>
+        <v>11200.34</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8960.27</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>11140.35</v>
+        <v>11200.34</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2359.53</v>
+        <v>2372.23</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>22280.7</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2361.75</v>
+        <v>2374.47</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2785.09</v>
+        <v>2800.09</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2785.09</v>
+        <v>2800.09</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>27797.4</v>
+        <v>27947.09</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>8355.26</v>
+        <v>8400.26</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>22280.7</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>22280.7</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>12307.86</v>
+        <v>12374.14</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2617.98</v>
+        <v>2632.08</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>11140.35</v>
+        <v>11200.34</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>4456.14</v>
+        <v>4480.14</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>10583.33</v>
+        <v>10640.32</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2562.28</v>
+        <v>2576.08</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2673.68</v>
+        <v>2688.08</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>6684.21</v>
+        <v>6720.2</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2359.12</v>
+        <v>2371.83</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>23208.69</v>
+        <v>23333.67</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2395.18</v>
+        <v>2421.96</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5570.17</v>
+        <v>5632.47</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5570.17</v>
+        <v>5632.47</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>9011.950000000001</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>5570.17</v>
+        <v>5632.47</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>33421.05</v>
+        <v>33794.82</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2450.88</v>
+        <v>2478.29</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>50131.57</v>
+        <v>50692.23</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3787.72</v>
+        <v>3830.08</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>5362.31</v>
+        <v>5422.28</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5013.16</v>
+        <v>5069.22</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7241.23</v>
+        <v>7322.21</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2663.89</v>
+        <v>2693.68</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>10583.33</v>
+        <v>10701.69</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>25622.8</v>
+        <v>25909.36</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>6684.21</v>
+        <v>6758.96</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>13925.44</v>
+        <v>14081.18</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>22183.36</v>
+        <v>22431.45</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>6625.88</v>
+        <v>6699.98</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>22280.7</v>
+        <v>22529.88</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>11140.35</v>
+        <v>11264.94</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>18938.59</v>
+        <v>19150.4</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>3592.76</v>
+        <v>3632.94</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>16710.52</v>
+        <v>16897.41</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>7909.65</v>
+        <v>7998.11</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>6461.4</v>
+        <v>6533.67</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>69070.17</v>
+        <v>69842.63</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>7798.24</v>
+        <v>7885.46</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>27850.87</v>
+        <v>28162.35</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>16320.61</v>
+        <v>16503.14</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>6684.21</v>
+        <v>6758.96</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>21166.66</v>
+        <v>21403.39</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>55701.75</v>
+        <v>56324.7</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>11140.35</v>
+        <v>11264.94</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>15596.49</v>
+        <v>15770.92</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2450.88</v>
+        <v>2478.29</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>5124.56</v>
+        <v>5181.87</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>3342.1</v>
+        <v>3379.48</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3342.1</v>
+        <v>3379.48</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>4456.14</v>
+        <v>4505.98</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>9011.950000000001</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>11140.35</v>
+        <v>11224.73</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3119.3</v>
+        <v>3142.92</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>33421.05</v>
+        <v>33674.19</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2540</v>
+        <v>2559.24</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.89</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>16710.52</v>
+        <v>16837.1</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2450.88</v>
+        <v>2469.44</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>5570.17</v>
+        <v>5612.37</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>14482.45</v>
+        <v>14592.15</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>5570.17</v>
+        <v>5612.37</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>24508.77</v>
+        <v>24694.41</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3342.1</v>
+        <v>3367.42</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>26402.63</v>
+        <v>26602.61</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4567.54</v>
+        <v>4602.14</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2359.12</v>
+        <v>2376.99</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>6582.98</v>
+        <v>6632.84</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3342.1</v>
+        <v>3367.42</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>18938.59</v>
+        <v>19082.04</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>55701.75</v>
+        <v>56123.65</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>5570.17</v>
+        <v>5612.37</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>16710.52</v>
+        <v>16837.1</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>6684.21</v>
+        <v>6734.84</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3342.1</v>
+        <v>3367.42</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.89</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2361.75</v>
+        <v>2379.64</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.89</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>37877.19</v>
+        <v>38164.08</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.66</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>16710.52</v>
+        <v>16837.1</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.66</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2562.28</v>
+        <v>2581.69</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>11140.35</v>
+        <v>11224.73</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>17267.54</v>
+        <v>17398.33</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>3342.1</v>
+        <v>3367.42</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>20609.65</v>
+        <v>20765.75</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>6038.07</v>
+        <v>6083.8</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>7798.24</v>
+        <v>7827.79</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>4456.14</v>
+        <v>4473.02</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2359.12</v>
+        <v>2368.06</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>5395.27</v>
+        <v>5415.71</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3342.1</v>
+        <v>3354.77</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>3531.49</v>
+        <v>3544.87</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>14482.45</v>
+        <v>14537.32</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>6655.23</v>
+        <v>6680.45</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>14254.08</v>
+        <v>14308.08</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>22280.7</v>
+        <v>22365.11</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>3342.1</v>
+        <v>3354.77</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2390.72</v>
+        <v>2399.78</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>4456.14</v>
+        <v>4473.02</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>4099.65</v>
+        <v>4115.18</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3007.89</v>
+        <v>3019.29</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>13368.42</v>
+        <v>13419.07</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>8761.879999999999</v>
+        <v>8795.08</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>3899.12</v>
+        <v>3913.89</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2361.75</v>
+        <v>2370.7</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>4456.14</v>
+        <v>4473.02</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>22280.7</v>
+        <v>22365.11</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>5570.17</v>
+        <v>5591.28</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>5859.82</v>
+        <v>5882.02</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>22813.21</v>
+        <v>22899.64</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8946.040000000001</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>7863.97</v>
+        <v>7893.77</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>4344.74</v>
+        <v>4361.2</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>22280.7</v>
+        <v>22365.11</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>4456.14</v>
+        <v>4473.02</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>7798.24</v>
+        <v>7827.79</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2785.09</v>
+        <v>2795.64</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>17557.19</v>
+        <v>17623.71</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>2359.12</v>
+        <v>2368.06</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>5570.17</v>
+        <v>5591.28</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>5570.17</v>
+        <v>5591.28</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2562.28</v>
+        <v>2571.99</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2450.88</v>
+        <v>2460.16</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>23156.02</v>
+        <v>23243.75</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2785.09</v>
+        <v>2795.64</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>12430.4</v>
+        <v>12477.5</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>6684.21</v>
+        <v>6709.53</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2359.12</v>
+        <v>2353.17</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3019.03</v>
+        <v>3011.41</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>5570.17</v>
+        <v>5556.11</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>11140.35</v>
+        <v>11112.22</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>5570.17</v>
+        <v>5556.11</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>6684.21</v>
+        <v>6667.33</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>8355.26</v>
+        <v>8334.17</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3342.1</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3342.1</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2450.88</v>
+        <v>2444.69</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2475.33</v>
+        <v>2469.08</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>8454.41</v>
+        <v>8433.07</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2729.39</v>
+        <v>2722.49</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2361.75</v>
+        <v>2355.79</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>10026.31</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>11140.35</v>
+        <v>11112.22</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2785.09</v>
+        <v>2778.06</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>38991.22</v>
+        <v>38892.78</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2409.91</v>
+        <v>2403.83</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>16710.52</v>
+        <v>16668.33</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2562.28</v>
+        <v>2555.81</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>6684.21</v>
+        <v>6667.33</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2360.12</v>
+        <v>2354.16</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>6684.21</v>
+        <v>6667.33</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2359.12</v>
+        <v>2353.17</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>3342.1</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>77627.35000000001</v>
+        <v>77431.35000000001</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8889.780000000001</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>2785.09</v>
+        <v>2778.06</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>13368.27</v>
+        <v>13334.52</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>27850.87</v>
+        <v>27780.56</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>42753.15</v>
+        <v>42645.21</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>13368.42</v>
+        <v>13334.67</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>33421.05</v>
+        <v>33336.67</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2361.75</v>
+        <v>2355.79</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>8745.74</v>
+        <v>8723.66</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4846.05</v>
+        <v>4833.82</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>7798.24</v>
+        <v>7778.56</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>3342.1</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>22889.91</v>
+        <v>22832.12</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>6229.29</v>
+        <v>6213.56</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>3676.32</v>
+        <v>3667.03</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>3899.12</v>
+        <v>3889.28</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>4456.14</v>
+        <v>4444.89</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>5570.17</v>
+        <v>5556.11</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>4456.14</v>
+        <v>4444.89</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>37877.19</v>
+        <v>37781.56</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>3640.58</v>
+        <v>3631.39</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8889.780000000001</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>4456.14</v>
+        <v>4498.48</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>5570.17</v>
+        <v>5623.1</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>38445.35</v>
+        <v>38810.6</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2359.12</v>
+        <v>2381.54</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>13702.63</v>
+        <v>13832.81</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2464.25</v>
+        <v>2487.66</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>4456.14</v>
+        <v>4498.48</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>11140.35</v>
+        <v>11246.19</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>7798.24</v>
+        <v>7872.33</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>3342.1</v>
+        <v>3373.86</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>6684.21</v>
+        <v>6747.71</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>16153.51</v>
+        <v>16306.98</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2359.15</v>
+        <v>2381.56</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>16710.52</v>
+        <v>16869.29</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2395.18</v>
+        <v>2417.93</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8996.950000000001</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>6684.21</v>
+        <v>6747.71</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>27850.87</v>
+        <v>28115.48</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3342.1</v>
+        <v>3373.86</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>14482.45</v>
+        <v>14620.05</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>22280.7</v>
+        <v>22492.38</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>11697.37</v>
+        <v>11808.5</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>50131.57</v>
+        <v>50607.86</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2450.88</v>
+        <v>2474.16</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>5570.17</v>
+        <v>5623.1</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>8021.05</v>
+        <v>8097.26</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>47123.68</v>
+        <v>47571.39</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>20052.63</v>
+        <v>20243.14</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8996.950000000001</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>2785.09</v>
+        <v>2811.55</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2785.09</v>
+        <v>2811.55</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2361.75</v>
+        <v>2384.19</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>3342.1</v>
+        <v>3373.86</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>35649.12</v>
+        <v>35987.81</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>13368.42</v>
+        <v>13495.43</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>12365.79</v>
+        <v>12483.27</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>7863.75</v>
+        <v>7938.46</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>16710.52</v>
+        <v>16869.29</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>5263.82</v>
+        <v>5303.03</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.34</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.34</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>2785.09</v>
+        <v>2805.84</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2450.88</v>
+        <v>2469.14</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2785.09</v>
+        <v>2805.84</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>2450.88</v>
+        <v>2469.14</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>12200.91</v>
+        <v>12291.81</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.17</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>3342.1</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>16710.52</v>
+        <v>16835.02</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2617.98</v>
+        <v>2637.49</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.34</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2785.09</v>
+        <v>2805.84</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2450.88</v>
+        <v>2469.14</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>5347.37</v>
+        <v>5387.21</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>8091.68</v>
+        <v>8151.96</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>13591.79</v>
+        <v>13693.05</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>6684.21</v>
+        <v>6734.01</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2450.88</v>
+        <v>2469.14</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>16710.52</v>
+        <v>16835.02</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>5570.17</v>
+        <v>5611.67</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>13368.42</v>
+        <v>13468.01</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>3342.1</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.17</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>11140.35</v>
+        <v>11223.34</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>14482.45</v>
+        <v>14590.35</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>3049.11</v>
+        <v>3071.83</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>3475.79</v>
+        <v>3501.68</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>2601.84</v>
+        <v>2621.22</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>2389.81</v>
+        <v>2407.61</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>5570.17</v>
+        <v>5611.67</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>2450.88</v>
+        <v>2469.14</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>11140.35</v>
+        <v>11223.34</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2359.53</v>
+        <v>2377.1</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>16130.6</v>
+        <v>16250.77</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>6610.92</v>
+        <v>6660.17</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>27442.02</v>
+        <v>27646.46</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>13368.42</v>
+        <v>13468.01</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3342.1</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.17</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.17</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>2450.88</v>
+        <v>2469.14</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>13368.42</v>
+        <v>13468.01</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>11140.35</v>
+        <v>11223.34</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>13479.82</v>
+        <v>13580.25</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>10026.31</v>
+        <v>10101.01</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>18938.59</v>
+        <v>19079.69</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>5570.17</v>
+        <v>5611.67</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>6684.21</v>
+        <v>6617.55</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>11140.35</v>
+        <v>11029.25</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>9141.309999999999</v>
+        <v>9050.139999999999</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>3342.1</v>
+        <v>3308.77</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>5570.17</v>
+        <v>5514.62</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>3342.1</v>
+        <v>3308.77</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>6684.21</v>
+        <v>6617.55</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>22280.7</v>
+        <v>22058.5</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>4790.1</v>
+        <v>4742.32</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>55701.75</v>
+        <v>55146.25</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>7628.91</v>
+        <v>7552.83</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>4456.14</v>
+        <v>4411.7</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8823.4</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>3119.3</v>
+        <v>3088.19</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>6962.72</v>
+        <v>6893.28</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8823.4</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>2450.88</v>
+        <v>2426.43</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>3342.1</v>
+        <v>3308.77</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>27850.87</v>
+        <v>27573.12</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>3342.1</v>
+        <v>3308.77</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>4456.14</v>
+        <v>4411.7</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>2361.75</v>
+        <v>2338.2</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>4456.14</v>
+        <v>4411.7</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>6684.21</v>
+        <v>6617.55</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>3378.73</v>
+        <v>3345.04</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>5681.43</v>
+        <v>5624.77</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>5570.17</v>
+        <v>5514.62</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>2785.09</v>
+        <v>2757.31</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>28586.14</v>
+        <v>28301.05</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>18381.58</v>
+        <v>18198.26</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>5665.31</v>
+        <v>5608.81</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>75963.37</v>
+        <v>75205.81</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>6684.21</v>
+        <v>6617.55</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>8729.01</v>
+        <v>8641.959999999999</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>2562.28</v>
+        <v>2536.73</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>2359.12</v>
+        <v>2335.6</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>24954.38</v>
+        <v>24705.52</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>11140.35</v>
+        <v>11029.25</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>4456.14</v>
+        <v>4411.7</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>267368.39</v>
+        <v>264701.99</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>2395.18</v>
+        <v>2371.29</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>5570.17</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8873.209999999999</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>4456.14</v>
+        <v>4436.61</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>33421.05</v>
+        <v>33274.55</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>5570.17</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>5570.17</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>32864.03</v>
+        <v>32719.97</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>4456.14</v>
+        <v>4436.61</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>4456.14</v>
+        <v>4436.61</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>61271.92</v>
+        <v>61003.34</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>4456.14</v>
+        <v>4436.61</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>12254.38</v>
+        <v>12200.67</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>2799.12</v>
+        <v>2786.85</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>11363.51</v>
+        <v>11313.7</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>2785.09</v>
+        <v>2772.88</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>5124.56</v>
+        <v>5102.1</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>23394.73</v>
+        <v>23292.18</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>22280.7</v>
+        <v>22183.03</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>4456.14</v>
+        <v>4436.61</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>6684.21</v>
+        <v>6654.91</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>28964.91</v>
+        <v>28837.94</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>47216.26</v>
+        <v>47009.29</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>5570.17</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>3899.12</v>
+        <v>3882.03</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>5570.17</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>2783.97</v>
+        <v>2771.77</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>46789.47</v>
+        <v>46584.37</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>2450.88</v>
+        <v>2440.13</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>2450.88</v>
+        <v>2440.13</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>3342.1</v>
+        <v>3327.45</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>3528.97</v>
+        <v>3513.51</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>3314.25</v>
+        <v>3299.73</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>9391.309999999999</v>
+        <v>9350.15</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2693.16</v>
+        <v>2681.35</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>33933.5</v>
+        <v>33784.76</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>7798.24</v>
+        <v>7764.06</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>12765.73</v>
+        <v>12709.77</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>22280.7</v>
+        <v>22183.03</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>7798.24</v>
+        <v>7764.06</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8815.33</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>3342.1</v>
+        <v>3305.75</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>39657.46</v>
+        <v>39226.06</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>4734.65</v>
+        <v>4683.14</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>2450.88</v>
+        <v>2424.22</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>15039.47</v>
+        <v>14875.87</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>36985.96</v>
+        <v>36583.62</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2785.09</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>37320.17</v>
+        <v>36914.19</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>3119.3</v>
+        <v>3085.37</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>5570.17</v>
+        <v>5509.58</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>3342.1</v>
+        <v>3305.75</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>2359.12</v>
+        <v>2333.46</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>3342.1</v>
+        <v>3305.75</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>7863.86</v>
+        <v>7778.32</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>22280.7</v>
+        <v>22038.32</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>11140.35</v>
+        <v>11019.16</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2785.09</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>33421.05</v>
+        <v>33057.49</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>3342.1</v>
+        <v>3305.75</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>4456.14</v>
+        <v>4407.66</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>14482.45</v>
+        <v>14324.91</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>2450.88</v>
+        <v>2424.22</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>2361.75</v>
+        <v>2336.06</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>2785.09</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>5570.17</v>
+        <v>5509.58</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>5570.17</v>
+        <v>5509.58</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>2785.09</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>6684.21</v>
+        <v>6611.5</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>11140.35</v>
+        <v>11019.16</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>33421.05</v>
+        <v>33057.49</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>33421.05</v>
+        <v>33057.49</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>7798.24</v>
+        <v>7713.41</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>13368.42</v>
+        <v>13222.99</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>7575.44</v>
+        <v>7493.03</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>9357.889999999999</v>
+        <v>9256.1</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>5570.17</v>
+        <v>5509.58</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2450.88</v>
+        <v>2424.22</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>16710.52</v>
+        <v>16528.74</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>9918.110000000001</v>
+        <v>9810.219999999999</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>5013.16</v>
+        <v>4958.62</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>12430.4</v>
+        <v>12295.18</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>3342.1</v>
+        <v>3305.75</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>2785.09</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>4678.95</v>
+        <v>4628.05</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>11697.37</v>
+        <v>11570.12</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>5213.84</v>
+        <v>5157.13</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>7895.87</v>
+        <v>7809.98</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>6684.21</v>
+        <v>6611.5</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>55701.75</v>
+        <v>55095.81</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>2359.12</v>
+        <v>2333.46</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>10026.31</v>
+        <v>9917.25</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>16710.52</v>
+        <v>16672.59</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>11140.35</v>
+        <v>11115.06</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>6684.21</v>
+        <v>6669.04</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>13368.42</v>
+        <v>13338.08</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>13368.42</v>
+        <v>13338.08</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>44561.4</v>
+        <v>44460.25</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>4456.14</v>
+        <v>4446.03</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>10026.31</v>
+        <v>10003.56</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>5570.17</v>
+        <v>5557.53</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>11140.35</v>
+        <v>11115.06</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>14036.84</v>
+        <v>14004.98</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>16710.52</v>
+        <v>16672.59</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>2785.09</v>
+        <v>2778.77</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>6446.27</v>
+        <v>6431.64</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>4456.14</v>
+        <v>4446.03</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>8076.75</v>
+        <v>8058.42</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>22280.7</v>
+        <v>22230.13</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>11028.95</v>
+        <v>11003.91</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>6684.21</v>
+        <v>6669.04</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>11792.62</v>
+        <v>11765.85</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>4456.14</v>
+        <v>4445.14</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>23394.73</v>
+        <v>23336.96</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>4456.14</v>
+        <v>4445.14</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2361.75</v>
+        <v>2355.92</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>2450.88</v>
+        <v>2444.82</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>3899.12</v>
+        <v>3889.49</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>6461.4</v>
+        <v>6445.45</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>2450.88</v>
+        <v>2444.82</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>2450.88</v>
+        <v>2444.82</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>25622.8</v>
+        <v>25559.53</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>4456.14</v>
+        <v>4445.14</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>36763.15</v>
+        <v>36672.37</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2450.88</v>
+        <v>2444.82</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>2785.09</v>
+        <v>2778.21</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>2359.12</v>
+        <v>2353.3</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>2896.49</v>
+        <v>2889.34</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>11140.35</v>
+        <v>11112.84</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>6684.21</v>
+        <v>6667.7</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>4790.35</v>
+        <v>4813.88</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>5570.17</v>
+        <v>5597.54</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>22280.7</v>
+        <v>22390.15</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8956.059999999999</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>12254.38</v>
+        <v>12314.58</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>6684.21</v>
+        <v>6717.04</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>22280.7</v>
+        <v>22390.15</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>2361.75</v>
+        <v>2373.36</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>2785.09</v>
+        <v>2798.77</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>3342.1</v>
+        <v>3358.52</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>7798.24</v>
+        <v>7836.55</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>6684.21</v>
+        <v>6717.04</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>4456.14</v>
+        <v>4478.03</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>5570.17</v>
+        <v>5597.54</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>2785.09</v>
+        <v>2798.77</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>38434.21</v>
+        <v>38623.01</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>3342.1</v>
+        <v>3358.52</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>2361.75</v>
+        <v>2373.36</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>11140.35</v>
+        <v>11195.07</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>5013.16</v>
+        <v>5037.78</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>2450.88</v>
+        <v>2462.92</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>31409.97</v>
+        <v>31564.26</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>2359.12</v>
+        <v>2370.71</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>7241.23</v>
+        <v>7276.8</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>8355.26</v>
+        <v>8396.309999999999</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>33421.05</v>
+        <v>33585.22</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>13368.42</v>
+        <v>13434.09</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>3509.21</v>
+        <v>3526.45</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>5570.17</v>
+        <v>5597.54</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>13368.42</v>
+        <v>13434.09</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>7798.24</v>
+        <v>7836.55</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>2673.68</v>
+        <v>2686.82</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>11140.35</v>
+        <v>11195.07</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>7798.24</v>
+        <v>7836.55</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>46789.47</v>
+        <v>47019.31</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>12430.4</v>
+        <v>12491.46</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>2359.12</v>
+        <v>2370.71</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>11140.35</v>
+        <v>11195.07</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>21166.66</v>
+        <v>21270.64</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>7798.24</v>
+        <v>7836.55</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>2785.09</v>
+        <v>2798.77</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>16710.52</v>
+        <v>16765.96</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>3342.1</v>
+        <v>3353.19</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>6684.21</v>
+        <v>6706.38</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>5570.17</v>
+        <v>5588.65</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>11140.35</v>
+        <v>11177.31</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>25622.8</v>
+        <v>25707.8</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>2896.49</v>
+        <v>2906.1</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>4351.42</v>
+        <v>4365.86</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>11140.35</v>
+        <v>11177.31</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>5013.16</v>
+        <v>5029.79</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>3676.32</v>
+        <v>3688.51</v>
       </c>
     </row>
     <row r="647">
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>3342.1</v>
+        <v>3353.19</v>
       </c>
     </row>
     <row r="648">
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>3342.1</v>
+        <v>3353.19</v>
       </c>
     </row>
     <row r="649">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>7798.24</v>
+        <v>7824.11</v>
       </c>
     </row>
     <row r="650">
@@ -40101,7 +40101,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>59998.6</v>
+        <v>60197.63</v>
       </c>
     </row>
     <row r="651">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>22280.7</v>
+        <v>22354.61</v>
       </c>
     </row>
     <row r="652">
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>16710.52</v>
+        <v>16765.96</v>
       </c>
     </row>
     <row r="653">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>64021.08</v>
+        <v>64233.46</v>
       </c>
     </row>
     <row r="654">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>2785.09</v>
+        <v>2794.33</v>
       </c>
     </row>
     <row r="655">
@@ -40406,7 +40406,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>2366.21</v>
+        <v>2374.06</v>
       </c>
     </row>
     <row r="656">
@@ -40467,7 +40467,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>10026.31</v>
+        <v>10059.58</v>
       </c>
     </row>
     <row r="657">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>11140.35</v>
+        <v>11177.31</v>
       </c>
     </row>
     <row r="658">
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>5208.2</v>
+        <v>5225.48</v>
       </c>
     </row>
     <row r="659">
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>9469.299999999999</v>
+        <v>9500.709999999999</v>
       </c>
     </row>
     <row r="660">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>2785.09</v>
+        <v>2794.33</v>
       </c>
     </row>
     <row r="661">
@@ -40772,7 +40772,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>16710.52</v>
+        <v>16765.96</v>
       </c>
     </row>
     <row r="662">
@@ -40833,7 +40833,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>2359.53</v>
+        <v>2367.35</v>
       </c>
     </row>
     <row r="663">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>3342.1</v>
+        <v>3353.19</v>
       </c>
     </row>
     <row r="664">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>2562.28</v>
+        <v>2570.78</v>
       </c>
     </row>
     <row r="665">
@@ -41016,7 +41016,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>2361.75</v>
+        <v>2369.59</v>
       </c>
     </row>
     <row r="666">
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>3119.3</v>
+        <v>3129.65</v>
       </c>
     </row>
     <row r="667">
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>31192.98</v>
+        <v>31296.46</v>
       </c>
     </row>
     <row r="668">
@@ -41199,7 +41199,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>7686.84</v>
+        <v>7712.34</v>
       </c>
     </row>
     <row r="669">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>7863.97</v>
+        <v>7890.06</v>
       </c>
     </row>
     <row r="670">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>77851.12</v>
+        <v>78109.38</v>
       </c>
     </row>
     <row r="671">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>33421.05</v>
+        <v>33531.92</v>
       </c>
     </row>
     <row r="672">
@@ -41443,7 +41443,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>55701.75</v>
+        <v>55886.53</v>
       </c>
     </row>
     <row r="673">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>12254.38</v>
+        <v>12295.04</v>
       </c>
     </row>
     <row r="674">
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>4456.14</v>
+        <v>4470.92</v>
       </c>
     </row>
     <row r="675">
@@ -41626,7 +41626,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2359.53</v>
+        <v>2367.35</v>
       </c>
     </row>
     <row r="676">
@@ -41687,7 +41687,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>3342.1</v>
+        <v>3353.19</v>
       </c>
     </row>
     <row r="677">
@@ -41748,7 +41748,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8941.84</v>
       </c>
     </row>
     <row r="678">
@@ -41809,7 +41809,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>11140.35</v>
+        <v>11177.31</v>
       </c>
     </row>
     <row r="679">
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>8766.34</v>
+        <v>8794.24</v>
       </c>
     </row>
     <row r="680">
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>19229.79</v>
+        <v>19290.99</v>
       </c>
     </row>
     <row r="681">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>2469.12</v>
+        <v>2476.97</v>
       </c>
     </row>
     <row r="682">
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>6684.21</v>
+        <v>6705.48</v>
       </c>
     </row>
     <row r="683">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>11140.35</v>
+        <v>11175.81</v>
       </c>
     </row>
     <row r="684">
@@ -42175,7 +42175,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>36763.15</v>
+        <v>36880.16</v>
       </c>
     </row>
     <row r="685">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>22280.7</v>
+        <v>22351.61</v>
       </c>
     </row>
     <row r="686">
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>55701.75</v>
+        <v>55879.03</v>
       </c>
     </row>
     <row r="687">
@@ -42358,7 +42358,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>3342.1</v>
+        <v>3352.74</v>
       </c>
     </row>
     <row r="688">
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>3397.58</v>
+        <v>3408.4</v>
       </c>
     </row>
     <row r="689">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>22280.7</v>
+        <v>22351.61</v>
       </c>
     </row>
     <row r="690">
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>2785.09</v>
+        <v>2793.95</v>
       </c>
     </row>
     <row r="691">
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>44561.4</v>
+        <v>44703.23</v>
       </c>
     </row>
     <row r="692">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>3342.1</v>
+        <v>3352.74</v>
       </c>
     </row>
     <row r="693">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>18938.59</v>
+        <v>18998.87</v>
       </c>
     </row>
     <row r="694">
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>2450.88</v>
+        <v>2458.68</v>
       </c>
     </row>
     <row r="695">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>6684.21</v>
+        <v>6705.48</v>
       </c>
     </row>
     <row r="696">
@@ -42907,7 +42907,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>12682.62</v>
+        <v>12722.99</v>
       </c>
     </row>
     <row r="697">
@@ -42968,7 +42968,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>2450.88</v>
+        <v>2458.68</v>
       </c>
     </row>
     <row r="698">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>5013.16</v>
+        <v>5029.11</v>
       </c>
     </row>
     <row r="699">
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>3345.06</v>
+        <v>3355.71</v>
       </c>
     </row>
     <row r="700">
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8940.65</v>
       </c>
     </row>
     <row r="701">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>13368.42</v>
+        <v>13410.97</v>
       </c>
     </row>
     <row r="702">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8940.65</v>
       </c>
     </row>
     <row r="703">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>6684.21</v>
+        <v>6705.48</v>
       </c>
     </row>
     <row r="704">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>2359.12</v>
+        <v>2366.63</v>
       </c>
     </row>
     <row r="705">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>4728.57</v>
+        <v>4743.62</v>
       </c>
     </row>
     <row r="706">
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>14482.45</v>
+        <v>14528.55</v>
       </c>
     </row>
     <row r="707">
@@ -43578,7 +43578,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>27850.87</v>
+        <v>27939.52</v>
       </c>
     </row>
     <row r="708">
@@ -43639,7 +43639,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>4456.14</v>
+        <v>4470.32</v>
       </c>
     </row>
     <row r="709">
@@ -43700,7 +43700,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>3139.28</v>
+        <v>3149.27</v>
       </c>
     </row>
     <row r="710">
@@ -43761,7 +43761,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>38991.22</v>
+        <v>39115.32</v>
       </c>
     </row>
     <row r="711">
@@ -43822,7 +43822,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>4456.14</v>
+        <v>4470.32</v>
       </c>
     </row>
     <row r="712">
@@ -43883,7 +43883,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>11140.35</v>
+        <v>11175.81</v>
       </c>
     </row>
     <row r="713">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>7241.23</v>
+        <v>7264.27</v>
       </c>
     </row>
     <row r="714">
@@ -44005,7 +44005,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>15596.49</v>
+        <v>15646.13</v>
       </c>
     </row>
     <row r="715">
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>2395.18</v>
+        <v>2402.8</v>
       </c>
     </row>
     <row r="716">
@@ -44127,7 +44127,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>11140.35</v>
+        <v>11175.81</v>
       </c>
     </row>
     <row r="717">
@@ -44188,7 +44188,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>2361.75</v>
+        <v>2369.27</v>
       </c>
     </row>
     <row r="718">
@@ -44249,7 +44249,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>2450.88</v>
+        <v>2458.68</v>
       </c>
     </row>
     <row r="719">
@@ -44310,7 +44310,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>5570.17</v>
+        <v>5599.79</v>
       </c>
     </row>
     <row r="720">
@@ -44371,7 +44371,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>3392.57</v>
+        <v>3410.61</v>
       </c>
     </row>
     <row r="721">
@@ -44432,7 +44432,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>6910.45</v>
+        <v>6947.19</v>
       </c>
     </row>
     <row r="722">
@@ -44493,7 +44493,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>3342.1</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="723">
@@ -44554,7 +44554,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>22280.7</v>
+        <v>22399.18</v>
       </c>
     </row>
     <row r="724">
@@ -44615,7 +44615,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>5570.17</v>
+        <v>5599.79</v>
       </c>
     </row>
     <row r="725">
@@ -44676,7 +44676,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>22280.7</v>
+        <v>22399.18</v>
       </c>
     </row>
     <row r="726">
@@ -44737,7 +44737,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>6684.21</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="727">
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>17824.56</v>
+        <v>17919.34</v>
       </c>
     </row>
     <row r="728">
@@ -44859,7 +44859,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>3342.1</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="729">
@@ -44920,7 +44920,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>3899.12</v>
+        <v>3919.86</v>
       </c>
     </row>
     <row r="730">
@@ -44981,7 +44981,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>3342.1</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="731">
@@ -45042,7 +45042,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>4010.53</v>
+        <v>4031.85</v>
       </c>
     </row>
     <row r="732">
@@ -45103,7 +45103,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>7798.24</v>
+        <v>7839.71</v>
       </c>
     </row>
     <row r="733">
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>8394.25</v>
+        <v>8438.889999999999</v>
       </c>
     </row>
     <row r="734">
@@ -45225,7 +45225,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>3342.1</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="735">
@@ -45286,7 +45286,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>5347.37</v>
+        <v>5375.8</v>
       </c>
     </row>
     <row r="736">
@@ -45347,7 +45347,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>4456.14</v>
+        <v>4479.84</v>
       </c>
     </row>
     <row r="737">
@@ -45408,7 +45408,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>26736.84</v>
+        <v>26879.01</v>
       </c>
     </row>
     <row r="738">
@@ -45469,7 +45469,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>6684.21</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="739">
@@ -45530,7 +45530,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8959.67</v>
       </c>
     </row>
     <row r="740">
@@ -45591,7 +45591,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>30078.94</v>
+        <v>30238.89</v>
       </c>
     </row>
     <row r="741">
@@ -45652,7 +45652,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>35649.12</v>
+        <v>35838.68</v>
       </c>
     </row>
     <row r="742">
@@ -45713,7 +45713,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>7798.24</v>
+        <v>7839.71</v>
       </c>
     </row>
     <row r="743">
@@ -45774,7 +45774,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>3899.12</v>
+        <v>3919.86</v>
       </c>
     </row>
     <row r="744">
@@ -45835,7 +45835,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>6684.21</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="745">
@@ -45896,7 +45896,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>2359.12</v>
+        <v>2371.67</v>
       </c>
     </row>
     <row r="746">
@@ -45957,7 +45957,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>2406.32</v>
+        <v>2419.11</v>
       </c>
     </row>
     <row r="747">
@@ -46018,7 +46018,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>3342.1</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="748">
@@ -46079,7 +46079,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>2813.85</v>
+        <v>2828.81</v>
       </c>
     </row>
     <row r="749">
@@ -46140,7 +46140,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>33421.05</v>
+        <v>33598.76</v>
       </c>
     </row>
     <row r="750">
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>78637.5</v>
+        <v>79055.64999999999</v>
       </c>
     </row>
     <row r="751">
@@ -46262,7 +46262,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>5570.17</v>
+        <v>5599.79</v>
       </c>
     </row>
     <row r="752">
@@ -46323,7 +46323,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>6684.21</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="753">
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>6461.4</v>
+        <v>6495.76</v>
       </c>
     </row>
     <row r="754">
@@ -46445,7 +46445,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>2785.09</v>
+        <v>2799.9</v>
       </c>
     </row>
     <row r="755">
@@ -46506,7 +46506,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>2450.88</v>
+        <v>2463.91</v>
       </c>
     </row>
     <row r="756">
@@ -46567,7 +46567,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>11140.35</v>
+        <v>11199.59</v>
       </c>
     </row>
     <row r="757">
@@ -46628,7 +46628,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>11140.35</v>
+        <v>11199.59</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/suministro-de-combustibles/may-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28746,7 +28746,7 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29345,7 +29345,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -30077,7 +30077,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30443,7 +30443,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30504,7 +30504,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31968,7 +31968,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32761,7 +32761,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33371,7 +33371,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -34042,7 +34042,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34164,7 +34164,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -35567,7 +35567,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -36665,7 +36665,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -37153,7 +37153,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37336,7 +37336,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37397,7 +37397,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37824,7 +37824,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38800,7 +38800,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -39715,7 +39715,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40813,7 +40813,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40935,7 +40935,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41972,7 +41972,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42094,7 +42094,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42460,7 +42460,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42521,7 +42521,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42826,7 +42826,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -43131,7 +43131,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43619,7 +43619,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43985,7 +43985,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44107,7 +44107,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44473,7 +44473,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -45327,7 +45327,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45693,7 +45693,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45876,7 +45876,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -46059,7 +46059,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46364,7 +46364,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -46486,7 +46486,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/may-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/may-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M757"/>
+  <dimension ref="A1:M758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Rosendo - Educación</t>
+          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Productivo y T</t>
+          <t>Corporación Municipal de Desarrollo Productivo y Turismo de Molina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Municipalidad de Yerbas Buenas-Depto. Salud</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tesorería Regional Concepción</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Antuco - Salud</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE EDUCACION - CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Tesorería Regional de V Región</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SLEP MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Proyecto San Joaquín</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUNTA ARENAS</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Cementerio General</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Trehuaco - Salud</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION VII REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16282,12 +16282,12 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16343,12 +16343,12 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Corporación del Deporte e Inclusión Social de la I</t>
+          <t>Corporación del Deporte e Inclusión Social de la Ilustre Municipalidad de Cerro Navia</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Des.Social C de Tango</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE CALERA DE TANGO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION V REGIÓN</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación de Magallanes</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20796,7 +20796,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Magalllanes y Antártica Chil</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -23541,7 +23541,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24151,7 +24151,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24212,7 +24212,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Zona de Bienestar "Coyhaique"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -24792,7 +24792,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>3621-152-CM26</t>
+          <t>3737-35-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -24812,22 +24812,22 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>3928.17</v>
+        <v>2621.22</v>
       </c>
     </row>
     <row r="401">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2737-286-CM26</t>
+          <t>3621-152-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -25056,17 +25056,17 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25091,13 +25091,13 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>3501.68</v>
+        <v>3928.17</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>3737-35-CM26</t>
+          <t>2737-286-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -25122,17 +25122,17 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>2621.22</v>
+        <v>3501.68</v>
       </c>
     </row>
     <row r="406">
@@ -25432,7 +25432,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Geologia y Mineria</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26408,7 +26408,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27445,7 +27445,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>SERPLAC V REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -28482,7 +28482,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -28791,7 +28791,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -28852,7 +28852,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -29162,7 +29162,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Proyecto La Cisterna</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -29645,7 +29645,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -30072,7 +30072,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30255,7 +30255,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -30377,7 +30377,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -30428,7 +30428,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -30560,7 +30560,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -30865,7 +30865,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>Municipalidad de Pemuco - Salud</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -30987,7 +30987,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -31109,7 +31109,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Municipalidad de Pemuco - Salud</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -31175,7 +31175,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31292,7 +31292,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -32085,7 +32085,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32268,7 +32268,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -32756,7 +32756,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -34342,7 +34342,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -34647,7 +34647,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -34891,7 +34891,7 @@
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -35074,7 +35074,7 @@
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36416,7 +36416,7 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -37148,7 +37148,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Departamento de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -37758,7 +37758,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Proyecto San Joaquín</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -37941,7 +37941,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>Departamento Comunal de Salud</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -38307,7 +38307,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLECO DEPARTAMENTO</t>
+          <t>I MUNICIPALIDAD DE QUILLECO</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -38917,7 +38917,7 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -39344,7 +39344,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -40381,7 +40381,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Antuco - Salud</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -40686,7 +40686,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>Comité de Des Productivo Regional Antofagasta</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -40991,7 +40991,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -41179,7 +41179,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41815,7 +41815,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>1087-115-CM26</t>
+          <t>1057535-252-CM26</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -41840,17 +41840,17 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.070-2</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL FUTA SRÜKA LAWENCHE KUNKO MAPU MO</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41870,13 +41870,13 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>8794.24</v>
+        <v>5029.11</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>2297-679-CM26</t>
+          <t>1087-115-CM26</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -41896,32 +41896,32 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K680" t="inlineStr"/>
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>19290.99</v>
+        <v>8794.24</v>
       </c>
     </row>
     <row r="681">
@@ -41998,7 +41998,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>3791-622-CM26</t>
+          <t>3678-170-CM26</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -42018,22 +42018,22 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42053,13 +42053,13 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>6705.48</v>
+        <v>22351.61</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>1777-56-CM26</t>
+          <t>3791-622-CM26</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -42084,17 +42084,17 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>60.804.012-9</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42114,13 +42114,13 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>11175.81</v>
+        <v>6705.48</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>1058345-30-CM26</t>
+          <t>1777-56-CM26</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -42145,17 +42145,17 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>60.804.012-9</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42175,13 +42175,13 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>36880.16</v>
+        <v>11175.81</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>3678-170-CM26</t>
+          <t>2297-679-CM26</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -42206,27 +42206,27 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K685" t="inlineStr"/>
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>22351.61</v>
+        <v>19290.99</v>
       </c>
     </row>
     <row r="686">
@@ -42974,7 +42974,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>1057535-252-CM26</t>
+          <t>1058345-30-CM26</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -42999,17 +42999,17 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>61.980.070-2</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>HOSPITAL FUTA SRÜKA LAWENCHE KUNKO MAPU MO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>5029.11</v>
+        <v>36880.16</v>
       </c>
     </row>
     <row r="699">
@@ -43096,7 +43096,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2663-304-CM26</t>
+          <t>1220203-39-CM26</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -43116,32 +43116,32 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K700" t="inlineStr"/>
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>8940.65</v>
+        <v>3149.27</v>
       </c>
     </row>
     <row r="701">
@@ -43187,7 +43187,7 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -43309,7 +43309,7 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -43401,7 +43401,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2297-657-CM26</t>
+          <t>2663-304-CM26</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -43421,22 +43421,22 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>4743.62</v>
+        <v>8940.65</v>
       </c>
     </row>
     <row r="706">
@@ -43645,7 +43645,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>1220203-39-CM26</t>
+          <t>2297-657-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -43670,27 +43670,27 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K709" t="inlineStr"/>
@@ -43700,7 +43700,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>3149.27</v>
+        <v>4743.62</v>
       </c>
     </row>
     <row r="710">
@@ -43919,7 +43919,7 @@
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -43980,7 +43980,7 @@
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -44041,7 +44041,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Delegación Provincial Chiloe</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -44133,7 +44133,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>5178-2183-CM26</t>
+          <t>1480160-5-CM26</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -44153,22 +44153,22 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44188,13 +44188,13 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>2369.27</v>
+        <v>2458.68</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>1480160-5-CM26</t>
+          <t>5178-2183-CM26</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -44214,22 +44214,22 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>corporacion de Asistencia Judicial  del Biobío</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44249,13 +44249,13 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>2458.68</v>
+        <v>2369.27</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>4406-441-CM26</t>
+          <t>3502-236-CM26</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -44280,12 +44280,12 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -44310,13 +44310,13 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>5599.79</v>
+        <v>22399.18</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>4476-66-CM26</t>
+          <t>1057385-157-CM26</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -44341,27 +44341,27 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K720" t="inlineStr"/>
@@ -44371,13 +44371,13 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>3410.61</v>
+        <v>5599.79</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>5413-488-CM26</t>
+          <t>3807-225-CM26</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -44402,27 +44402,27 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.120.200-3</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K721" t="inlineStr"/>
@@ -44432,13 +44432,13 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>6947.19</v>
+        <v>22399.18</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>1426098-132-CM26</t>
+          <t>4406-441-CM26</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -44458,32 +44458,32 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K722" t="inlineStr"/>
@@ -44493,13 +44493,13 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>3359.88</v>
+        <v>5599.79</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>3807-225-CM26</t>
+          <t>5413-488-CM26</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -44524,27 +44524,27 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K723" t="inlineStr"/>
@@ -44554,13 +44554,13 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>22399.18</v>
+        <v>6947.19</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>1057385-157-CM26</t>
+          <t>4476-66-CM26</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -44585,27 +44585,27 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K724" t="inlineStr"/>
@@ -44615,13 +44615,13 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>5599.79</v>
+        <v>3410.61</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>3502-236-CM26</t>
+          <t>1426098-132-CM26</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -44641,32 +44641,32 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K725" t="inlineStr"/>
@@ -44676,13 +44676,13 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>22399.18</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>557974-208-CM26</t>
+          <t>520149-76-CM26</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -44707,17 +44707,17 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>70.878.900-3</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y ATENCION AL MENOR,</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -44737,13 +44737,13 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>6719.75</v>
+        <v>5375.8</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>2923-408-CM26</t>
+          <t>3707-284-CM26</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -44768,17 +44768,17 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>17919.34</v>
+        <v>8438.889999999999</v>
       </c>
     </row>
     <row r="728">
@@ -44865,7 +44865,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>3743-164-CM26</t>
+          <t>557974-208-CM26</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -44890,17 +44890,17 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>70.878.900-3</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y ATENCION AL MENOR,</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -44920,13 +44920,13 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>3919.86</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>1057553-200-CM26</t>
+          <t>3743-164-CM26</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -44951,17 +44951,17 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -44981,13 +44981,13 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>3359.88</v>
+        <v>3919.86</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>1558-183-CM26</t>
+          <t>1057553-200-CM26</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -45012,17 +45012,17 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45042,13 +45042,13 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>4031.85</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>3747-145-CM26</t>
+          <t>1558-183-CM26</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -45068,22 +45068,22 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45103,13 +45103,13 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>7839.71</v>
+        <v>4031.85</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>3707-284-CM26</t>
+          <t>3747-145-CM26</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -45129,22 +45129,22 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45164,13 +45164,13 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>8438.889999999999</v>
+        <v>7839.71</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>1746-127-CM26</t>
+          <t>2311-162-CM26</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -45195,17 +45195,17 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45225,13 +45225,13 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>3359.88</v>
+        <v>4479.84</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>520149-76-CM26</t>
+          <t>1746-127-CM26</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -45256,17 +45256,17 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45286,13 +45286,13 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>5375.8</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>3656-328-CM26</t>
+          <t>2923-408-CM26</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -45312,22 +45312,22 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>69.081.300-9</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE REQUINOA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45347,13 +45347,13 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>4479.84</v>
+        <v>17919.34</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>3834-150-CM26</t>
+          <t>3656-328-CM26</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -45373,22 +45373,22 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.081.300-9</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45408,13 +45408,13 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>26879.01</v>
+        <v>4479.84</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>3035-230-CM26</t>
+          <t>3834-150-CM26</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -45434,22 +45434,22 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45469,13 +45469,13 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>6719.75</v>
+        <v>26879.01</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>1376-359-CM26</t>
+          <t>3035-230-CM26</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -45495,22 +45495,22 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -45530,13 +45530,13 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>8959.67</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2455-85-CM26</t>
+          <t>1376-359-CM26</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -45561,17 +45561,17 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -45591,13 +45591,13 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>30238.89</v>
+        <v>8959.67</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>3666-17-CM26</t>
+          <t>2455-85-CM26</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -45622,12 +45622,12 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>69.071.600-3</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIL TIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -45652,13 +45652,13 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>35838.68</v>
+        <v>30238.89</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2080-4857-CM26</t>
+          <t>3666-17-CM26</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -45683,17 +45683,17 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>69.071.600-3</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE TIL TIL</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45713,13 +45713,13 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>7839.71</v>
+        <v>35838.68</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>3343-132-CM26</t>
+          <t>2080-4857-CM26</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -45744,17 +45744,17 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>69.061.200-3</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLMUE</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45774,13 +45774,13 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>3919.86</v>
+        <v>7839.71</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>3809-41-CM26</t>
+          <t>3343-132-CM26</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -45800,22 +45800,22 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>69.061.200-3</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>I MUNICIPALIDAD DE OLMUE</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -45835,13 +45835,13 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>6719.75</v>
+        <v>3919.86</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>1057543-900-CM26</t>
+          <t>3809-41-CM26</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -45866,27 +45866,27 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>61.607.201-3</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K745" t="inlineStr"/>
@@ -45896,13 +45896,13 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>2371.67</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>5423-223-CM26</t>
+          <t>1057543-900-CM26</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -45922,22 +45922,22 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -45957,13 +45957,13 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>2419.11</v>
+        <v>2371.67</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>568658-905-CM26</t>
+          <t>5423-223-CM26</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -45988,27 +45988,27 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K747" t="inlineStr"/>
@@ -46018,13 +46018,13 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>3359.88</v>
+        <v>2419.11</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>3177-163-CM26</t>
+          <t>568658-905-CM26</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -46049,27 +46049,27 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K748" t="inlineStr"/>
@@ -46079,13 +46079,13 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>2828.81</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>1159-116-CM26</t>
+          <t>3177-163-CM26</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -46105,32 +46105,32 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K749" t="inlineStr"/>
@@ -46140,13 +46140,13 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>33598.76</v>
+        <v>2828.81</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2595-217-CM26</t>
+          <t>1159-116-CM26</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -46166,22 +46166,22 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46201,13 +46201,13 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>79055.64999999999</v>
+        <v>33598.76</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>4328-507-CM26</t>
+          <t>2595-217-CM26</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -46227,22 +46227,22 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46262,13 +46262,13 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>5599.79</v>
+        <v>79055.64999999999</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2500-84-CM26</t>
+          <t>4328-507-CM26</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -46288,22 +46288,22 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46323,13 +46323,13 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>6719.75</v>
+        <v>5599.79</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>4738-132-CM26</t>
+          <t>2500-84-CM26</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -46354,17 +46354,17 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46384,13 +46384,13 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>6495.76</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>1650-232-CM26</t>
+          <t>4738-132-CM26</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -46410,32 +46410,32 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>61.602.204-0</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>Hospital Santa Juana</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K754" t="inlineStr"/>
@@ -46445,13 +46445,13 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>2799.9</v>
+        <v>6495.76</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>4493-306-CM26</t>
+          <t>1650-232-CM26</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -46471,17 +46471,17 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>69.150.502-2</t>
+          <t>61.602.204-0</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>Hospital Santa Juana</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -46491,12 +46491,12 @@
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K755" t="inlineStr"/>
@@ -46506,13 +46506,13 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>2463.91</v>
+        <v>2799.9</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>4328-508-CM26</t>
+          <t>4493-306-CM26</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -46532,22 +46532,22 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>69.150.502-2</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -46567,13 +46567,13 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>11199.59</v>
+        <v>2463.91</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>3904-428-CM26</t>
+          <t>4328-508-CM26</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -46588,7 +46588,7 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
@@ -46598,12 +46598,12 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -46628,6 +46628,67 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
+        <v>11199.59</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>3904-428-CM26</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>69.141.200-8</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BULNES</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr"/>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M758" s="2" t="n">
         <v>11199.59</v>
       </c>
     </row>

--- a/docs/oc-mensuales/suministro-de-combustibles/may-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +24027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +24092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +24157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +24222,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +24352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24417,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24742,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24807,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +25002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +25067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +25132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +25197,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +25262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25327,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25977,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +26042,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +26107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +26172,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +26237,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +26302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +27017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +27082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +27147,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +27212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +27277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +27342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +28057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +28122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +28187,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +28252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +28317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +28382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28577,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +29032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +29097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +29162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +29227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +29292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +29357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29682,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29747,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +30007,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +30072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +30137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +30202,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +30267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +30332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +30397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +30722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +30852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +31047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +31112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29297,7 +31177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +31242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29419,7 +31307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +31372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +31437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +31502,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +31567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +31632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +31697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +32022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +32087,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +32152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +32217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +32282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +32347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +32412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +32477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +32542,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +33062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +33127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +33192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +33257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +33322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +33387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +33452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +33517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +33582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +33712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +33972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +34037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +34102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +34167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +34232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +34297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +34362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +34427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32408,7 +34492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +34557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +34622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32591,7 +34687,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32774,7 +34882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32835,7 +34947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +35012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +35077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +35142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33079,7 +35207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +35272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +35337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +35402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33323,7 +35467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +35532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +35597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33506,7 +35662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33567,7 +35727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33689,7 +35857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +36052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +36117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +36182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34055,7 +36247,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +36312,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +36377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +36442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +36507,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +36572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +36637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34482,7 +36702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +37027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +37092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +37157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34970,7 +37222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +37287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35092,7 +37352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +37417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +37482,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +37547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35336,7 +37612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +37677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35702,7 +38002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35763,7 +38067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +38132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35885,7 +38197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +38262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +38327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +38392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +38457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +38522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36251,7 +38587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +38652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +38717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +38847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +38912,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36617,7 +38977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +39042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +39107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +39172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +39237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36922,7 +39302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +39367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37044,7 +39432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +39497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +39562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +39627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37288,7 +39692,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +39757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +39822,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +39887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +40017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +40082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +40147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +40212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37837,7 +40277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37898,7 +40342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +40407,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +40472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38081,7 +40537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +40602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +40667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +40732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +40927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +41057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +41122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +41187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +41252,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +41317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +41382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +41447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +41512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +41577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +41642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39179,7 +41707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39240,7 +41772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39301,7 +41837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +41902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +41967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +42032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +42097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39606,7 +42162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +42227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +42292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +42357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39850,7 +42422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +42487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +42552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40033,7 +42617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +42682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +42747,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +42812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40277,7 +42877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40338,7 +42942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40399,7 +43007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40460,7 +43072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40521,7 +43137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40582,7 +43202,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40643,7 +43267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40704,7 +43332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40765,7 +43397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40826,7 +43462,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40887,7 +43527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40948,7 +43592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41009,7 +43657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41070,7 +43722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41131,7 +43787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41192,7 +43852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41253,7 +43917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41314,7 +43982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41375,7 +44047,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41436,7 +44112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +44177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41558,7 +44242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41619,7 +44307,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +44372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41741,7 +44437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41802,7 +44502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41863,7 +44567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41924,7 +44632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41985,7 +44697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42046,7 +44762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42107,7 +44827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42168,7 +44892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42229,7 +44957,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +45022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42351,7 +45087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42412,7 +45152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42473,7 +45217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42534,7 +45282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42595,7 +45347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42656,7 +45412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42717,7 +45477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +45542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +45607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42900,7 +45672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42961,7 +45737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +45802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43083,7 +45867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43144,7 +45932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43205,7 +45997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43266,7 +46062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43327,7 +46127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43388,7 +46192,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43449,7 +46257,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43510,7 +46322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43571,7 +46387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43632,7 +46452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43693,7 +46517,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43754,7 +46582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43815,7 +46647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43876,7 +46712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43937,7 +46777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43998,7 +46842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44059,7 +46907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44120,7 +46972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44181,7 +47037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44242,7 +47102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44303,7 +47167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44364,7 +47232,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44425,7 +47297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44486,7 +47362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44547,7 +47427,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44608,7 +47492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44669,7 +47557,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44730,7 +47622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44791,7 +47687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44852,7 +47752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44913,7 +47817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44974,7 +47882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45035,7 +47947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45096,7 +48012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45157,7 +48077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45218,7 +48142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45279,7 +48207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45340,7 +48272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45401,7 +48337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45462,7 +48402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45523,7 +48467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45584,7 +48532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45645,7 +48597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45706,7 +48662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45767,7 +48727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45828,7 +48792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45889,7 +48857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45950,7 +48922,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46011,7 +48987,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46072,7 +49052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46133,7 +49117,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46194,7 +49182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46255,7 +49247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46316,7 +49312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46377,7 +49377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46438,7 +49442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46499,7 +49507,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46560,7 +49572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46621,7 +49637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46682,7 +49702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
